--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.883495145631068</v>
+        <v>0.8543689320388349</v>
       </c>
       <c r="C14" t="n">
         <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E14" t="n">
         <v>0.8712871287128713</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8586605906772955</v>
+        <v>0.8558433229935229</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6</v>
+        <v>0.5553030303030303</v>
       </c>
       <c r="C15" t="n">
         <v>0.5384615384615384</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5282608695652175</v>
+        <v>0.5782608695652174</v>
       </c>
       <c r="E15" t="n">
         <v>0.5664794007490637</v>
       </c>
       <c r="F15" t="n">
-        <v>0.558300452193955</v>
+        <v>0.5596262097697124</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6347517730496454</v>
+        <v>0.565156206023079</v>
       </c>
       <c r="C16" t="n">
         <v>0.5380952380952381</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5213675213675213</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="E16" t="n">
         <v>0.5825119236883943</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5691816140501997</v>
+        <v>0.5694000256251472</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8483784342078082</v>
+        <v>0.8164958369653431</v>
       </c>
       <c r="C17" t="n">
         <v>0.8273932253313697</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7576312576312576</v>
+        <v>0.7886297376093294</v>
       </c>
       <c r="E17" t="n">
         <v>0.8472225282941649</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8201563613661501</v>
+        <v>0.8199353320500518</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6655303030303029</v>
+        <v>0.6689393939393938</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6373626373626373</v>
+        <v>0.5989010989010989</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7195652173913044</v>
+        <v>0.7282608695652175</v>
       </c>
       <c r="E18" t="n">
         <v>0.737827715355805</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6900714682850124</v>
+        <v>0.6834822694403788</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[88, 0], [12, 3]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[88, 4], [18, 2]]</t>
+          <t>[[88, 4], [16, 4]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1406,34 +1406,34 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8586605906772955</v>
+        <v>0.8558433229935229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03210042517171322</v>
+        <v>0.02146550655085346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.558300452193955</v>
+        <v>0.5596262097697124</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02784648321281685</v>
+        <v>0.01467012239705122</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5691816140501997</v>
+        <v>0.5694000256251472</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04395933670832542</v>
+        <v>0.02045316303022275</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8201563613661501</v>
+        <v>0.8199353320500518</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03705004583251274</v>
+        <v>0.02116649251048098</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6900714682850124</v>
+        <v>0.6834822694403788</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04040739418687493</v>
+        <v>0.05550680174203569</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,16 +613,16 @@
         <v>0.8155339805825242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="E8" t="n">
         <v>0.8514851485148515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8296781990637401</v>
+        <v>0.832600695381855</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.8367424242424242</v>
       </c>
       <c r="C9" t="n">
-        <v>0.695054945054945</v>
+        <v>0.7394688644688645</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7130434782608696</v>
+        <v>0.7467391304347826</v>
       </c>
       <c r="E9" t="n">
         <v>0.8436329588014981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7721184515899342</v>
+        <v>0.7916458444868923</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.7298826777087646</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7015384615384616</v>
+        <v>0.7474556213017751</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6818181818181819</v>
+        <v>0.691051528191548</v>
       </c>
       <c r="E10" t="n">
         <v>0.7408041060735671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7135108567847438</v>
+        <v>0.7272984833189137</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8376851796016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.863695479777954</v>
+        <v>0.884665405965961</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7987012987012987</v>
+        <v>0.7956762976623949</v>
       </c>
       <c r="E11" t="n">
         <v>0.8699319889217322</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8425034867506462</v>
+        <v>0.8469897180379221</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.9037878787878788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8534798534798534</v>
+        <v>0.9148351648351649</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8619565217391304</v>
+        <v>0.8853260869565218</v>
       </c>
       <c r="E12" t="n">
         <v>0.9138576779026217</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8832704829773711</v>
+        <v>0.9044517021205468</v>
       </c>
     </row>
     <row r="13">
@@ -726,12 +726,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[78, 6], [7, 6]]</t>
+          <t>[[79, 5], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[76, 16], [8, 12]]</t>
+          <t>[[73, 19], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 13], [5, 10]]</t>
+          <t>[[75, 14], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8296781990637401</v>
+        <v>0.832600695381855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03132971225514219</v>
+        <v>0.04086229822491089</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7721184515899342</v>
+        <v>0.7916458444868923</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06840909862072556</v>
+        <v>0.04867086338654412</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7135108567847438</v>
+        <v>0.7272984833189137</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02324178280371042</v>
+        <v>0.0218473789863963</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8425034867506462</v>
+        <v>0.8469897180379221</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02803244130249666</v>
+        <v>0.03415203800765652</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8832704829773711</v>
+        <v>0.9044517021205468</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02597261333483749</v>
+        <v>0.01185873618032526</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[75, 13], [5, 10]]</t>
+          <t>[[75, 14], [4, 11]]</t>
         </is>
       </c>
     </row>
